--- a/Backend/public/docs/clientes-personas-format.xlsx
+++ b/Backend/public/docs/clientes-personas-format.xlsx
@@ -39,9 +39,9 @@
     <definedName name="Municipios_4">'Municipios'!$B$13:$B$15</definedName>
     <definedName name="Municipios_5">'Municipios'!$B$16:$B$21</definedName>
     <definedName name="Municipios_6">'Municipios'!$B$22:$B$26</definedName>
-    <definedName name="Municipios_7">'"Municipios'!$B$27:$B$28"</definedName>
-    <definedName name="Municipios_8">'"Municipios'!$B$29:$B$31"</definedName>
     <definedName name="Municipios_9">'Municipios'!$B$32:$B$33</definedName>
+    <definedName name="Municipios_7">'Municipios'!$B$27:$B$28</definedName>
+    <definedName name="Municipios_8">'Municipios'!$B$29:$B$31</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
@@ -15589,9006 +15589,15 @@
       <c r="T1000"/>
     </row>
   </sheetData>
-  <dataValidations count="3000">
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G763">
+  <dataValidations count="3">
+    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="G2:G1000">
       <formula1>Departamentos!$B$2:$B$16</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G695">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
+    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="I2:I1000">
+      <formula1>'Distritos'!$B$2:$B$263</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G740">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G867">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G857">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G811">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G56">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G474">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G778">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G91">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G36">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G628">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G821">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G703">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G206">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G342">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G367">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G580">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G354">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G571">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G693">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G319">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G385">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G546">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G551">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G412">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G297">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G54">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G787">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G534">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G752">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G368">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G194">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G498">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G936">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G331">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G186">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G887">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G75">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G941">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G98">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G159">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G338">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G200">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G4">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G530">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G449">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G137">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G112">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G419">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G931">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G156">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G995">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G384">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G765">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G840">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G757">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G171">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G320">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G227">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G261">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G361">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G783">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G620">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G684">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G442">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G744">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G661">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G597">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G836">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G111">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G145">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G147">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G989">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G427">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G140">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G422">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G768">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G750">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G615">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G85">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G245">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G704">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G69">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G938">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G800">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G901">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G691">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G884">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G1">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G852">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G815">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G956">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G592">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G554">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G93">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G308">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G346">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G57">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G15">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G31">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G946">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G659">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G846">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G890">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G794">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G859">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G722">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G476">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G687">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G180">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G642">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G256">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G178">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G428">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G425">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G351">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G218">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G64">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G646">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G805">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G216">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G463">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G930">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G985">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G937">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G767">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G267">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G107">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G215">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G500">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G622">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G276">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G798">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G246">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G879">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G332">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G880">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G82">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G607">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G480">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G6">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G904">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G587">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G128">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G439">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G507">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G417">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G18">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G796">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G928">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G163">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G835">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G655">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G631">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G639">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G277">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G122">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G708">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G736">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G625">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G677">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G43">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G70">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G436">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G812">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G777">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G324">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G817">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G205">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G755">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G528">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G826">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G871">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G853">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G461">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G881">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G865">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G226">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G897">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G386">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G689">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G283">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G753">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G357">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G289">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G754">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G742">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G692">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G165">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G784">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G489">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G413">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G394">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G160">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G569">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G786">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G833">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G782">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G553">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G942">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G618">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G275">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G264">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G564">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G999">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G797">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G885">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G329">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G804">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G856">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G954">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G398">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G922">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G672">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G103">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G994">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G866">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G713">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G99">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G286">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G741">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G411">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G988">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G512">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G348">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G868">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G60">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G959">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G262">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G20">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G270">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G10">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G718">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G421">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G735">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G219">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G919">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G602">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G633">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G182">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G188">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G745">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G645">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G743">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G492">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G444">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G388">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G14">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G158">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G395">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G468">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G503">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G278">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G849">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G668">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G373">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G992">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G834">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G191">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G636">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G601">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G720">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G886">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G430">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G177">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G121">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G146">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G345">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G155">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G738">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G86">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G450">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G58">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G305">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G41">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G729">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G707">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G423">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G899">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G827">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G818">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G149">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G731">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G486">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G108">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G16">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G822">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G47">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G905">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G851">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G649">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G567">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G791">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G771">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G667">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G772">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G97">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G287">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G280">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G81">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G477">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G27">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G584">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G624">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G671">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G610">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G924">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G556">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G608">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G134">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G221">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G25">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G562">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G844">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G248">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G67">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G611">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G700">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G699">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G362">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G243">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G295">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G253">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G730">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G374">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G1000">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G907">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G967">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G606">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G843">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G204">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G2">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G258">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G209">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G279">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G435">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G120">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G365">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G343">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G114">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G605">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G263">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G813">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G501">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G42">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G393">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G199">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G238">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G759">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G970">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G335">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G630">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G770">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G838">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G207">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G109">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G682">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G347">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G945">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G152">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G913">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G566">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G957">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G762">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G50">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G572">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G400">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G958">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G33">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G548">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G948">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G681">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G858">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G506">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G323">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G714">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G77">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G30">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G685">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G455">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G185">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G926">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G73">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G525">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G917">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G22">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G168">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G749">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G333">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G66">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G208">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G990">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G397">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G950">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G876">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G212">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G978">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G612">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G678">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G198">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G603">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G453">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G179">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G260">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G966">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G788">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G848">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G987">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G535">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G581">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G247">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G241">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G32">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G136">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G557">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G391">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G955">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G829">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G732">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G747">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G828">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G976">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G802">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G932">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G665">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G641">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G969">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G330">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G92">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G268">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G918">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G706">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G814">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G239">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G951">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G5">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G516">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G482">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G854">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G583">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G383">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G249">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G61">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G773">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G698">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G65">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G366">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G273">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G124">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G658">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G375">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G820">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G793">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G138">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G705">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G727">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G490">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G192">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G9">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G403">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G837">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G269">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G415">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G341">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G440">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G172">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G62">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G485">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G964">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G184">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G855">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G499">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G176">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G84">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G363">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G328">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G609">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G968">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G538">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G79">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G483">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G29">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G34">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G3">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G344">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G481">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G586">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G935">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G321">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G7">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G529">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G318">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G139">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G505">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G632">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G446">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G196">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G154">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G893">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G728">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G303">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G656">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G653">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G469">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G795">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G541">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G807">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G883">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G460">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G961">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G457">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G195">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G288">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G561">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G161">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G380">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G233">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G688">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G470">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G748">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G314">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G676">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G515">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G861">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G549">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G761">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G627">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G792">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G669">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G864">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G943">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G364">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G975">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G88">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G76">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G169">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G173">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G23">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G285">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G242">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G563">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G157">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G475">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G74">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G982">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G284">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G431">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G514">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G652">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G531">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G434">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G129">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G523">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G11">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G95">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G125">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G458">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G921">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G896">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G971">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G181">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G369">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G402">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G382">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G131">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G737">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G595">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G349">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G38">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G214">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G45">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G467">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G40">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G508">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G888">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G299">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G933">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G719">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G892">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G986">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G132">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G903">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G164">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G340">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G26">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G558">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G686">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G24">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G702">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G352">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G874">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G282">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G785">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G560">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G894">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G593">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G429">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G307">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G673">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G585">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G734">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G379">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G574">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G311">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G51">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G189">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G377">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G266">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G565">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G438">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G170">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G552">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G89">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G790">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G150">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G573">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G963">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G816">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G240">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G17">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G494">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G591">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G337">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G113">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G830">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G911">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G716">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G550">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G697">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G353">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G915">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G766">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G780">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G923">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G983">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G657">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G701">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G271">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G462">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G87">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G638">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G666">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G53">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G522">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G670">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G407">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G872">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G758">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G520">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G293">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G806">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G543">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G465">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G230">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G123">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G71">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G228">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G598">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G96">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G555">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G927">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G944">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G325">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G533">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G495">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G133">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G372">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G544">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G441">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G675">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G63">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G960">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G493">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G823">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G680">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G912">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G135">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G715">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G117">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G49">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G356">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G90">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G46">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G274">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G406">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G517">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G292">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G401">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G236">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G94">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G370">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G488">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G466">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G312">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G799">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G213">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G229">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G984">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G909">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G640">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G44">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G294">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G115">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G910">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G202">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G291">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G126">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G623">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G613">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G570">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G616">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G779">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G479">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G456">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G878">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G537">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G52">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G416">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G925">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G939">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G21">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G217">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G151">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G973">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G317">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G809">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G934">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G302">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G127">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G902">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G272">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G68">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G110">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G889">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G381">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G617">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G590">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G13">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G511">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G839">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G775">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G825">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G873">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G694">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G252">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G596">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G244">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G265">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G651">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G723">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G650">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G447">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G190">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G211">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G664">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G663">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G257">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G119">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G496">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G471">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G683">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G378">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G201">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G774">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G808">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G389">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G604">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G724">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G589">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G175">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G19">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G643">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G80">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G448">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G143">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G281">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G162">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G721">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G906">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G433">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G410">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G355">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G360">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G746">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G644">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G310">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G862">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G545">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G870">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G454">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G497">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G166">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G940">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G621">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G231">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G510">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G350">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G518">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G404">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G304">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G443">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G536">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G339">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G979">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G619">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G313">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G789">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G478">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G600">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G100">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G306">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G141">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G405">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G542">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G116">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G845">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G519">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G847">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G860">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G712">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G952">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G725">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G824">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G648">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G726">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G539">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G769">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G102">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G193">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G225">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G895">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G900">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G801">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G547">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G599">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G28">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G977">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G142">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G451">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G459">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G484">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G540">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G568">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G764">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G810">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G259">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G130">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G334">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G709">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G996">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G326">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G831">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G626">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G491">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G396">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G420">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G250">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G614">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G579">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G255">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G167">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G972">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G875">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G472">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G322">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G654">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G908">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G72">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G832">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G803">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G298">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G949">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G55">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G981">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G509">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G187">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G877">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G733">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G424">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G390">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G197">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G387">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G819">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G717">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G290">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G37">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G980">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G559">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G399">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G309">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G916">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G637">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G841">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G629">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G153">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G296">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G148">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G35">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G452">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G371">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G863">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G998">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G696">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G418">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G174">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G582">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G504">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G882">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G974">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G12">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G376">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G929">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G751">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G526">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G315">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G301">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G842">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G203">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G760">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G781">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G953">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G962">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G234">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G634">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G756">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G993">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G521">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G106">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G575">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G662">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G232">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G524">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G464">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G426">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G674">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G105">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G78">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G850">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G8">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G223">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G237">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G251">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G914">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G635">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G532">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G739">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G577">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G690">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G118">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G432">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G527">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G776">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G991">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G224">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G39">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G183">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G408">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G898">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G210">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G965">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G997">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G711">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G920">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G101">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G336">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G710">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G316">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G647">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G437">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G254">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G578">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G588">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G48">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G358">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G891">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G359">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G660">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G487">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G869">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G947">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G513">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G327">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G502">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G235">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G220">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G473">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G576">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G392">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G445">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G144">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G679">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G409">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G222">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G104">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G83">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G414">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G594">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G300">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G59">
-      <formula1>Departamentos!$B$2:$B$16</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I105">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I460">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I102">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I815">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I264">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I788">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I677">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I236">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I409">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I438">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I759">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I367">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I634">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I655">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I840">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I786">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I250">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I471">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I21">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I28">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I506">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I308">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I800">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I339">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I447">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I225">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I798">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I26">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I502">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I968">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I213">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I223">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I116">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I941">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I999">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I724">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I267">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I559">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I309">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I369">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I916">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I165">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I661">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I239">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I389">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I211">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I126">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I950">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I234">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I18">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I928">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I521">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I946">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I698">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I301">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I60">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I746">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I421">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I319">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I299">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I356">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I560">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I834">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I757">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I111">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I552">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I830">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I555">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I4">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I231">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I780">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I912">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I77">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I633">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I679">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I171">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I763">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I864">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I249">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I191">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I603">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I849">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I720">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I240">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I178">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I176">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I479">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I277">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I440">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I848">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I378">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I904">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I386">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I134">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I457">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I513">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I526">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I196">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I427">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I914">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I452">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I960">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I794">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I128">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I229">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I337">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I938">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I847">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I431">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I448">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I238">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I667">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I257">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I27">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I30">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I761">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I694">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I933">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I9">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I459">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I467">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I493">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I979">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I944">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I158">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I81">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I697">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I56">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I805">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I871">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I769">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I522">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I648">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I982">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I342">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I741">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I563">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I756">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I430">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I295">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I851">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I260">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I701">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I843">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I841">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I475">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I388">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I31">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I302">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I344">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I718">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I973">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I666">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I857">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I738">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I501">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I279">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I16">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I646">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I785">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I728">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I520">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I376">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I778">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I410">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I918">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I473">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I889">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I284">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I812">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I444">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I424">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I103">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I898">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I691">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I953">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I779">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I57">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I745">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I795">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I948">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I406">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I53">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I989">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I478">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I7">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I341">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I837">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I525">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I115">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I580">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I771">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I212">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I511">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I142">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I216">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I37">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I811">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I527">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I282">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I863">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I41">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I192">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I995">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I233">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I544">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I548">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I734">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I468">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I87">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I109">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I638">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I996">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I861">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I856">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I365">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I379">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I50">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I966">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I589">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I373">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I541">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I96">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I671">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I68">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I221">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I43">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I900">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I254">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I368">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I613">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I331">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I416">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I48">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I29">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I642">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I664">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I919">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I836">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I640">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I487">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I880">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I218">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I425">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I662">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I100">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I59">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I343">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I852">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I8">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I372">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I823">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I321">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I93">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I635">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I172">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I803">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I205">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I131">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I733">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I381">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I395">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I668">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I682">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I621">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I631">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I967">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I583">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I326">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I412">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I891">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I599">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I652">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I507">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I647">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I310">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I94">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I152">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I669">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I895">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I139">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I866">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I104">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I695">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I601">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I262">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I497">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I935">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I689">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I420">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I643">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I160">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I287">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I572">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I833">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I184">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I901">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I799">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I67">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I443">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I97">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I489">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I956">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I820">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I509">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I408">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I883">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I760">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I480">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I528">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I244">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I703">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I554">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I751">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I358">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I766">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I869">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I744">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I434">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I161">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I713">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I715">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I298">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I887">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I615">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I777">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I286">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I230">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I402">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I114">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I15">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I790">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I503">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I844">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I170">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I523">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I649">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I449">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I762">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I327">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I729">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I185">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I782">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I290">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I259">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I515">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I181">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I650">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I271">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I69">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I722">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I495">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I396">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I141">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I608">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I123">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I663">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I76">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I561">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I680">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I808">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I627">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I255">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I784">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I514">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I670">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I484">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I783">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I865">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I546">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I228">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I630">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I858">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I594">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I274">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I764">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I150">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I129">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I587">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I153">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I392">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I921">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I397">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I674">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I949">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I202">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I474">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I737">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I550">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I873">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I472">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I585">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I266">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I419">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I804">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I942">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I853">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I969">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I626">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I954">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I582">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I17">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I276">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I173">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I838">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I162">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I816">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I832">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I586">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I214">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I130">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I518">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I607">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I936">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I188">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I315">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I328">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I312">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I101">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I807">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I978">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I842">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I179">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I241">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I657">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I940">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I1000">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I78">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I500">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I540">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I792">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I547">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I877">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I353">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I135">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I84">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I481">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I207">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I584">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I364">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I325">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I993">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I198">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I819">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I957">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I193">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I350">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I413">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I683">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I132">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I725">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I868">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I177">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I653">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I894">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I813">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I91">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I464">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I796">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I939">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I340">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I387">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I120">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I148">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I359">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I391">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I375">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I403">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I89">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I208">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I839">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I758">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I595">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I781">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I768">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I136">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I593">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I125">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I318">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I818">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I791">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I529">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I405">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I11">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I121">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I70">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I538">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I119">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I991">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I242">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I581">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I961">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I886">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I73">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I55">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I934">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I801">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I712">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I330">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I74">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I975">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I609">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I463">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I628">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I40">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I224">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I371">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I774">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I614">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I743">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I82">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I22">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I556">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I166">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I739">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I754">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I363">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I542">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I859">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I684">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I88">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I917">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I962">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I620">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I269">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I1">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I183">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I569">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I623">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I822">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I721">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I932">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I997">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I175">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I922">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I870">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I651">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I272">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I300">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I167">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I945">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I151">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I533">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I931">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I639">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I186">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I407">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I35">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I988">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I25">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I335">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I748">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I199">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I850">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I347">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I772">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I937">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I985">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I51">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I672">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I930">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I206">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I303">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I253">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I200">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I685">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I490">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I145">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I297">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I699">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I711">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I306">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I157">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I127">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I95">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I54">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I710">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I377">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I108">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I656">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I923">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I882">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I182">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I44">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I401">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I3">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I454">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I616">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I316">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I716">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I38">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I110">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I446">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I854">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I750">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I943">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I414">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I753">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I611">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I717">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I477">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I731">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I994">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I564">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I576">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I927">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I749">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I357">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I332">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I773">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I534">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I512">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I965">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I195">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I404">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I432">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I776">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I426">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I215">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I735">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I972">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I385">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I875">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I394">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I322">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I469">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I71">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I926">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I896">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I984">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I723">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I445">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I742">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I537">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I137">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I291">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I536">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I925">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I645">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I719">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I539">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I709">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I553">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I75">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I908">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I399">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I885">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I281">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I617">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I83">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I867">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I203">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I338">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I99">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I280">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I692">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I140">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I504">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I835">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I390">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I911">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I499">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I6">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I324">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I462">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I197">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I765">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I567">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I660">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I461">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I252">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I305">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I398">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I451">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I296">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I990">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I881">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I681">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I828">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I112">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I905">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I690">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I730">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I659">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I323">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I531">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I320">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I574">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I747">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I913">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I806">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I261">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I39">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I517">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I34">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I770">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I632">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I354">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I65">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I606">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I976">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I625">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I346">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I888">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I169">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I283">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I476">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I64">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I637">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I293">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I592">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I629">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I971">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I575">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I530">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I220">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I232">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I899">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I411">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I14">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I665">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I85">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I612">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I154">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I450">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I174">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I311">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I673">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I106">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I549">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I187">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I361">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I288">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I90">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I909">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I707">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I846">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I826">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I622">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I204">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I429">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I436">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I802">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I144">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I545">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I428">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I543">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I485">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I789">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I959">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I998">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I246">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I573">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I824">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I597">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I714">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I578">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I61">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I596">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I619">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I610">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I600">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I658">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I879">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I453">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I439">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I906">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I907">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I117">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I349">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I289">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I423">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I226">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I482">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I860">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I588">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I551">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I66">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I278">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I752">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I329">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I524">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I510">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I727">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I970">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I155">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I285">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I496">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I149">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I958">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I829">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I46">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I124">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I491">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I190">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I352">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I884">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I565">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I209">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I273">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I456">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I874">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I33">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I872">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I983">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I275">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I862">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I893">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I348">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I494">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I736">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I465">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I951">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I163">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I317">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I333">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I164">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I897">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I605">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I256">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I483">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I577">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I243">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I383">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I845">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I268">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I678">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I98">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I307">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I486">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I415">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I113">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I688">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I810">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I986">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I47">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I855">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I915">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I532">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I143">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I910">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I981">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I706">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I384">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I636">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I963">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I72">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I313">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I924">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I566">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I964">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I570">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I251">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I86">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I265">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I437">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I80">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I624">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I156">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I441">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I23">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I360">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I568">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I974">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I294">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I168">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I700">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I827">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I740">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I235">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I562">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I797">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I118">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I809">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I210">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I13">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I304">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I334">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I618">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I52">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I519">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I2">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I654">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I32">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I558">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I19">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I814">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I590">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I270">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I825">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I726">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I422">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I604">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I433">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I676">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I36">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I920">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I382">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I787">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I63">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I641">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I217">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I180">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I62">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I10">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I644">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I245">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I45">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I470">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I345">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I466">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I980">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I987">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I817">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I775">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I133">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I222">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I362">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I903">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I704">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I977">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I146">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I686">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I708">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I189">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I516">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I591">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I508">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I400">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I374">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I488">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I455">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I955">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I793">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I947">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I675">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I505">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I418">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I902">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I201">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I892">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I258">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I732">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I929">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I49">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I876">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I247">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I58">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I227">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I20">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I579">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I492">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I571">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I194">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I687">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I355">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I831">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I458">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I598">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I890">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I992">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I351">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I314">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I535">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I263">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I498">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I219">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I702">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I442">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I12">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I693">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I42">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I248">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I122">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I821">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I696">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I5">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I366">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I380">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I138">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I147">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I159">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I92">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I755">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I24">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I602">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I370">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I435">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I557">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I336">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I878">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I767">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I705">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I292">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I952">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I107">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I79">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I237">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I417">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I393">
-      <formula1>INDIRECT("Distritos_"&amp;$G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K577">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K75">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K98">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K987">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K149">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K302">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K541">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K753">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K735">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K418">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K691">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K219">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K831">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K292">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K906">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K540">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K133">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K872">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K143">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K290">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K682">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K28">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K438">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K982">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K593">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K294">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K522">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K572">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K250">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K184">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K96">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K54">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K731">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K927">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K994">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K971">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K524">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K677">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K214">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K843">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K599">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K539">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K780">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K856">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K262">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K400">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K591">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K193">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K205">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K100">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K661">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K390">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K430">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K589">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K519">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K344">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K786">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K179">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K759">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K217">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K709">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K253">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K822">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K562">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K237">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K584">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K897">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K996">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K273">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K444">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K615">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K747">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K183">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K431">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K93">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K77">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K779">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K676">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K356">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K4">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K950">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K234">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K207">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K472">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K902">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K915">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K378">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K394">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K556">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K808">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K346">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K69">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K652">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K489">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K949">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K858">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K693">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K212">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K801">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K846">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K254">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K969">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K470">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K286">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K201">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K159">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K744">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K800">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K889">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K481">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K502">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K706">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K1000">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K454">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K121">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K272">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K602">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K582">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K499">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K447">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K338">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K813">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K825">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K134">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K395">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K491">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K647">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K576">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K618">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K578">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K737">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K397">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K450">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K83">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K760">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K326">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K421">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K458">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K341">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K260">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K72">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K579">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K97">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K817">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K50">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K837">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K947">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K464">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K160">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K416">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K170">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K981">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K151">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K716">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K475">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K484">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K34">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K563">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K257">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K946">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K701">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K202">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K171">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K861">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K99">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K736">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K466">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K137">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K147">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K569">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K144">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K425">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K114">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K640">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K157">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K508">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K409">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K274">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K762">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K231">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K775">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K11">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K865">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K680">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K185">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K439">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K564">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K708">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K979">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K742">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K623">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K398">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K621">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K136">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K226">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K402">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K48">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K331">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K768">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K382">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K711">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K316">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K370">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K973">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K117">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K790">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K44">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K821">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K957">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K612">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K73">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K876">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K600">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K853">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K261">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K754">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K964">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K962">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K15">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K180">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K38">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K718">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K793">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K265">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K221">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K101">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K270">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K919">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K566">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K548">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K794">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K851">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K911">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K168">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K770">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K870">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K901">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K485">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K555">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K469">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K531">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K225">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K818">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K634">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K37">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K130">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K45">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K66">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K871">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K268">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K574">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K479">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K999">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K173">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K561">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K296">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K514">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K474">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K324">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K588">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K24">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K681">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K380">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K2">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K850">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K627">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K230">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K864">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K937">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K40">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K842">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K494">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K190">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K974">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K728">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K135">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K111">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K771">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K42">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K596">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K3">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K222">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K1">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K845">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K312">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K119">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K956">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K798">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K587">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K637">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K674">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K384">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K967">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K988">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K968">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K941">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K166">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K930">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K560">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K608">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K882">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K19">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K885">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K487">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K537">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K907">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K248">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K26">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K895">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K426">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K14">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K700">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K233">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K369">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K835">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K518">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K145">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K462">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K995">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K406">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K970">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K862">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K545">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K365">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K459">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K722">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K276">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K601">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K738">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K717">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K977">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K165">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K766">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K723">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K659">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K115">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K56">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K6">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K352">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K784">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K509">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K550">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K620">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K345">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K340">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K113">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K293">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K271">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K881">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K498">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K799">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K932">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K758">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K32">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K914">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K23">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K206">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K685">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K848">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K456">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K408">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K954">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K860">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K624">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K635">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K534">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K603">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K213">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K228">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K339">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K342">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K218">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K349">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K847">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K371">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K308">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K223">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K583">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K805">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K879">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K594">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K894">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K997">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K156">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K692">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K734">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K857">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K266">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K473">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K976">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K955">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K33">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K803">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K65">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K59">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K244">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K197">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K699">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K112">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K12">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K70">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K62">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K607">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K457">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K252">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K698">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K924">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K191">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K852">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K311">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K104">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K688">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K740">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K654">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K732">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K828">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K8">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K7">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K824">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K307">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K929">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K978">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K375">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K836">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K833">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K407">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K807">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K743">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K512">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K358">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K811">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K396">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K285">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K559">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K595">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K405">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K791">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K301">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K610">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K552">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K501">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K597">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K120">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K804">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K71">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K376">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K666">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K506">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K486">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K404">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K923">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K844">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K683">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K176">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K892">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K354">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K992">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K497">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K792">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K533">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K796">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K129">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K530">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K874">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K586">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K391">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K653">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K337">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K107">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K22">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K933">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K305">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K189">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K424">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K670">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K878">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K17">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K657">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K830">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K85">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K867">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K435">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K565">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K953">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K403">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K975">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K315">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K471">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K671">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K239">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K289">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K972">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K53">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K816">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K433">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K730">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K495">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K849">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K951">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K504">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K920">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K557">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K140">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K152">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K855">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K178">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K585">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K912">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K366">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K429">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K186">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K167">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K707">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K209">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K163">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K936">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K355">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K318">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K660">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K806">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K490">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K381">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K507">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K729">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K41">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K741">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K30">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K904">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K353">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K383">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K763">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K196">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K90">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K211">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K74">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K304">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K629">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K678">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K102">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K422">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K535">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K300">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K350">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K224">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K896">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K529">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K138">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K639">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K966">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K43">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K297">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K675">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K60">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K611">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K909">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K317">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K150">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K656">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K679">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K899">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K772">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K321">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K765">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K755">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K299">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K132">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K663">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K505">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K649">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K255">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K935">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K773">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K823">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K437">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K757">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K269">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K279">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K910">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K460">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K377">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K335">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K503">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K903">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K672">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K249">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K525">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K164">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K616">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K942">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K158">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K645">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K329">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K153">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K940">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K232">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K751">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K714">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K764">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K614">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K298">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K25">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K182">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K761">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K520">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K613">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K482">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K330">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K662">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K658">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K314">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K118">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K868">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K697">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K626">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K551">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K900">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K965">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K827">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K280">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K690">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K359">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K131">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K277">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K82">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K888">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K188">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K945">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K651">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K410">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K756">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K890">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K961">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K668">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K79">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K905">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K372">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K605">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K432">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K13">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K575">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K154">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K278">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K695">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K689">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K87">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K725">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K687">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K39">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K423">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K492">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K203">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K710">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K704">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K142">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K64">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K427">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K795">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K875">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K778">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K883">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K644">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K103">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K500">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K61">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K374">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K446">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K362">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K938">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K719">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K441">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K891">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K931">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K694">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K442">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K998">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K712">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K820">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K776">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K859">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K288">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K526">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K832">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K81">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K917">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K20">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K632">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K702">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K468">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K877">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K360">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K235">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K21">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K510">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K323">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K241">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K445">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K453">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K387">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K523">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K198">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K448">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K392">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K295">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K985">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K187">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K646">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K606">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K46">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K55">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K814">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K139">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K251">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K991">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K752">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K283">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K465">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K320">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K216">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K642">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K866">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K281">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K841">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K303">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K980">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K733">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K630">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K863">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K745">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K348">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K598">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K783">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K347">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K724">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K177">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K797">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K127">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K869">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K622">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K781">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K769">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K242">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K943">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K148">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K511">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K802">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K57">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K146">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K515">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K449">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K461">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K357">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K749">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K351">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K58">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K887">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K568">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K815">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K94">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K124">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K401">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K125">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K306">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K543">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K549">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K834">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K625">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K873">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K467">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K521">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K204">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K567">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K547">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K440">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K195">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K536">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K443">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K108">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K592">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K367">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K542">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K819">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K628">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K267">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K334">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K990">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K655">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K319">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K476">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K829">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K544">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K785">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K309">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K199">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K664">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K546">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K669">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K414">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K636">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K322">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K826">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K141">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K236">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K455">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K215">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K389">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K123">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K258">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K9">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K517">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K767">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K643">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K581">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K944">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K399">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K884">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K194">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K419">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K463">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K619">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K328">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K713">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K984">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K200">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K385">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K538">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K787">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K633">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K571">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K379">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K939">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K631">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K428">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K838">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K928">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K715">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K558">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K513">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K477">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K739">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K553">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K91">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K68">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K648">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K839">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K570">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K245">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K84">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K452">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K420">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K893">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K684">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K686">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K49">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K275">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K227">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K229">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K721">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K78">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K921">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K92">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K29">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K246">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K528">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K650">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K908">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K284">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K922">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K287">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K590">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K336">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K609">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K886">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K181">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K373">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K109">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K10">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K161">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K434">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K727">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K958">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K934">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K80">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K812">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K926">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K413">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K259">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K638">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K696">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K493">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K986">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K840">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K417">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K361">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K240">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K415">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K604">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K88">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K810">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K67">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K247">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K386">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K898">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K673">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K36">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K333">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K388">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K451">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K313">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K516">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K665">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K580">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K667">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K238">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K436">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K327">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K63">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K332">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K496">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K789">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K126">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K393">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K325">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K782">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K5">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K918">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K411">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K86">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K983">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K35">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K777">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K788">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K116">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K76">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K748">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K483">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K16">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K47">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K220">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K110">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K880">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K488">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K412">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K174">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K532">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K916">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K363">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K208">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K105">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K573">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K554">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K963">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K192">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K95">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K31">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K256">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K527">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K703">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K169">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K175">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K480">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K243">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K89">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K948">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K925">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K343">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K854">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K264">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K809">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K705">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K952">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K726">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K478">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K989">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K746">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K368">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K641">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K720">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K52">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K155">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K128">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K960">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K122">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K774">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K993">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K310">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K263">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K172">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K162">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K210">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K913">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K18">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K750">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K291">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K106">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K617">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K51">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K282">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K364">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K959">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K27">
-      <formula1>INDIRECT("Municipios_"&amp;G1)</formula1>
+    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="K2:K1000">
+      <formula1>'Municipios'!$B$2:$B$46</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
